--- a/tut_MLOps/ROADMAP.xlsx
+++ b/tut_MLOps/ROADMAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\tut_MLOps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5AD454-42BC-457C-A12C-8BC62F55D9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56106AE-3F5F-455B-8BB8-9ED300E93BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="1605" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="164">
   <si>
     <t>Phase</t>
   </si>
@@ -510,10 +510,13 @@
     <t>Status</t>
   </si>
   <si>
-    <t>EC2 Done</t>
-  </si>
-  <si>
     <t>Lecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC2 Done - API, Streamlit </t>
+  </si>
+  <si>
+    <t>Done in ML</t>
   </si>
 </sst>
 </file>
@@ -914,7 +917,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1249,7 +1252,9 @@
       <c r="F17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
@@ -1270,7 +1275,9 @@
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
@@ -1493,7 +1500,7 @@
         <v>109</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
